--- a/leads/out/nj-trades-leads.xlsx
+++ b/leads/out/nj-trades-leads.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$P$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$Q$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -494,9 +494,10 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,15 +568,20 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Source Notes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Retrieved</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Source ID</t>
         </is>
@@ -630,15 +636,20 @@
       <c r="M2" s="5" t="n"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>City taken from raw_address; Apollo returned no city field.</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>69e2fc4d3e5988000131a2a4</t>
         </is>
@@ -693,15 +704,20 @@
       <c r="M3" s="5" t="n"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>HVAC tool manufacturer, not a contractor.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>5cb333d8f651255d075fa168</t>
         </is>
@@ -754,17 +770,18 @@
         </is>
       </c>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>56e3e7ccf3e5bb4c74007649</t>
         </is>
@@ -819,15 +836,20 @@
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Acquired by Persona Triangle (Jan 2025).</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>5e56f7bcc43add000103cccf</t>
         </is>
@@ -880,17 +902,18 @@
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>691d436deb003e000104091a</t>
         </is>
@@ -945,15 +968,20 @@
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Concrete furnishings fabricator, not a trade contractor. Owned by Renovation Brands.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>54a135c769702d48e26cc900</t>
         </is>
@@ -1006,17 +1034,18 @@
         </is>
       </c>
       <c r="M8" s="5" t="n"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>67f78bbf0c90160021cc466c</t>
         </is>
@@ -1071,15 +1100,20 @@
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Facilities management firm subcontracting trades, not a trade contractor.</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>6049b34d41bcb10001e1e750</t>
         </is>
@@ -1132,17 +1166,18 @@
         </is>
       </c>
       <c r="M10" s="5" t="n"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>556d2e27736964127e4cab00</t>
         </is>
@@ -1195,17 +1230,18 @@
         </is>
       </c>
       <c r="M11" s="5" t="n"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>54a134be69702d2db437be00</t>
         </is>
@@ -1258,17 +1294,18 @@
         </is>
       </c>
       <c r="M12" s="5" t="n"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>5e57f47754322100017f91bc</t>
         </is>
@@ -1321,17 +1358,18 @@
         </is>
       </c>
       <c r="M13" s="5" t="n"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>6640847d7c561e0300b674a2</t>
         </is>
@@ -1384,17 +1422,18 @@
         </is>
       </c>
       <c r="M14" s="5" t="n"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>5f492b0159e72900e34327f6</t>
         </is>
@@ -1447,17 +1486,18 @@
         </is>
       </c>
       <c r="M15" s="5" t="n"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>5f490d6bf7fdfc000144752a</t>
         </is>
@@ -1510,17 +1550,18 @@
         </is>
       </c>
       <c r="M16" s="5" t="n"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>5a9d7c4ca6da98d954d9f820</t>
         </is>
@@ -1575,15 +1616,20 @@
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Acquired by Core Roofing Systems (2024).</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>556da06973696411de645901</t>
         </is>
@@ -1636,17 +1682,18 @@
         </is>
       </c>
       <c r="M18" s="5" t="n"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>55f61ea4f3e5bb1985005838</t>
         </is>
@@ -1699,17 +1746,18 @@
         </is>
       </c>
       <c r="M19" s="5" t="n"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>54a1c8eb74686945fa2eb810</t>
         </is>
@@ -1762,17 +1810,18 @@
         </is>
       </c>
       <c r="M20" s="5" t="n"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>6677b228347d480374cf64d0</t>
         </is>
@@ -1825,17 +1874,18 @@
         </is>
       </c>
       <c r="M21" s="5" t="n"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>5a9dc00ba6da98d95ff8f633</t>
         </is>
@@ -1890,15 +1940,20 @@
       <c r="M22" s="5" t="n"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Retail facility-support firm subcontracting trades.</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>54a1208869702d94a4f14302</t>
         </is>
@@ -1951,17 +2006,18 @@
         </is>
       </c>
       <c r="M23" s="5" t="n"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>678867f72f152f02cef1796d</t>
         </is>
@@ -2014,17 +2070,18 @@
         </is>
       </c>
       <c r="M24" s="5" t="n"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>5d3619ec80f93ec05029ef78</t>
         </is>
@@ -2077,17 +2134,18 @@
         </is>
       </c>
       <c r="M25" s="5" t="n"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>66da9a2f99e8ca01b2f79d3f</t>
         </is>
@@ -2140,17 +2198,18 @@
         </is>
       </c>
       <c r="M26" s="5" t="n"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>5fcaf822039d520001046bfd</t>
         </is>
@@ -2203,17 +2262,18 @@
         </is>
       </c>
       <c r="M27" s="5" t="n"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>5fc8ca541545aa00019266f8</t>
         </is>
@@ -2266,17 +2326,18 @@
         </is>
       </c>
       <c r="M28" s="5" t="n"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>54a11f5069702d97c1aaf401</t>
         </is>
@@ -2329,17 +2390,18 @@
         </is>
       </c>
       <c r="M29" s="5" t="n"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>54a1b1c174686940122ede08</t>
         </is>
@@ -2394,15 +2456,20 @@
       <c r="M30" s="5" t="n"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>City taken from raw_address; Apollo returned no city field.</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>5da3c8178c688900011d5d8c</t>
         </is>
@@ -2457,15 +2524,20 @@
       <c r="M31" s="5" t="n"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Concrete waste-management service, not a concrete contractor.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>5da489887ca76a0001973e35</t>
         </is>
@@ -2518,17 +2590,18 @@
         </is>
       </c>
       <c r="M32" s="5" t="n"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>5a9dd370a6da98d9466ff7fb</t>
         </is>
@@ -2581,17 +2654,18 @@
         </is>
       </c>
       <c r="M33" s="5" t="n"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>5ee1e6c4bf7502008c570d74</t>
         </is>
@@ -2644,17 +2718,18 @@
         </is>
       </c>
       <c r="M34" s="5" t="n"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>615ec93e92552d0001d25ae2</t>
         </is>
@@ -2707,17 +2782,18 @@
         </is>
       </c>
       <c r="M35" s="5" t="n"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>5e565167fcbbe4000180d0d2</t>
         </is>
@@ -2772,15 +2848,20 @@
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>City taken from raw_address; Apollo returned no city field.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>54a138db69702d231f412300</t>
         </is>
@@ -2835,15 +2916,20 @@
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Apollo reports state=New Jersey but raw_address says Montgomery County, Pennsylvania, ZIP 19446 and phone is a 610 PA area code. Likely a PA company; NJ geography filter will pass it incorrectly.</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>64210965f7370c0001d1a6cd</t>
         </is>
@@ -2896,17 +2982,18 @@
         </is>
       </c>
       <c r="M38" s="5" t="n"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>54a1982d74686945faaa3300</t>
         </is>
@@ -2959,17 +3046,18 @@
         </is>
       </c>
       <c r="M39" s="5" t="n"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>5edaa5cea7f5ea00018e7d16</t>
         </is>
@@ -3022,17 +3110,18 @@
         </is>
       </c>
       <c r="M40" s="5" t="n"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>61ad3e91a294f3000198acfd</t>
         </is>
@@ -3085,17 +3174,18 @@
         </is>
       </c>
       <c r="M41" s="5" t="n"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>6138ac5254ec1e00a4b0d6f6</t>
         </is>
@@ -3150,15 +3240,20 @@
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>HVAC equipment rep / controls integrator, not a trade contractor.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>5ed1edf16056fe0001ce145c</t>
         </is>
@@ -3213,15 +3308,20 @@
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Ready-mix supplier, not a concrete contractor.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>6504211ef74543000129cdd7</t>
         </is>
@@ -3274,17 +3374,18 @@
         </is>
       </c>
       <c r="M44" s="5" t="n"/>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>6620936337d16d0007bc1938</t>
         </is>
@@ -3339,15 +3440,20 @@
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>HVAC manufacturers' rep, not a contractor.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>5d338427a3ae6185115f0455</t>
         </is>
@@ -3400,17 +3506,18 @@
         </is>
       </c>
       <c r="M46" s="5" t="n"/>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>63e585ff044e2b0001e1a39f</t>
         </is>
@@ -3465,15 +3572,20 @@
       <c r="M47" s="5" t="n"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Apollo reports West Milford, New Jersey but the description says Crown Point, Indiana and the phone is a 219 Indiana area code. Likely an Indiana company; NJ geography filter will pass it incorrectly.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>57c4cf11a6da986a5f9d9c54</t>
         </is>
@@ -3526,17 +3638,18 @@
         </is>
       </c>
       <c r="M48" s="5" t="n"/>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>54a12a0569702d8eebae3902</t>
         </is>
@@ -3589,17 +3702,18 @@
         </is>
       </c>
       <c r="M49" s="5" t="n"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>5a9f698aa6da98d96d852341</t>
         </is>
@@ -3652,17 +3766,18 @@
         </is>
       </c>
       <c r="M50" s="5" t="n"/>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>5e55cf9d5b661e000154aafe</t>
         </is>
@@ -3715,17 +3830,18 @@
         </is>
       </c>
       <c r="M51" s="5" t="n"/>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>6620901ff23832000747c2e7</t>
         </is>
@@ -3778,17 +3894,18 @@
         </is>
       </c>
       <c r="M52" s="5" t="n"/>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>5e570745b5e1ae0001fab891</t>
         </is>
@@ -3841,17 +3958,18 @@
         </is>
       </c>
       <c r="M53" s="5" t="n"/>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>5da35343bc199c0001d32faa</t>
         </is>
@@ -3904,17 +4022,18 @@
         </is>
       </c>
       <c r="M54" s="5" t="n"/>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>6852423f1f0704000142b56c</t>
         </is>
@@ -3967,17 +4086,18 @@
         </is>
       </c>
       <c r="M55" s="5" t="n"/>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>64995c1b4bca0e00ef5abfe6</t>
         </is>
@@ -4030,17 +4150,18 @@
         </is>
       </c>
       <c r="M56" s="5" t="n"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>5fca4311e5e2c5000147f85d</t>
         </is>
@@ -4093,17 +4214,18 @@
         </is>
       </c>
       <c r="M57" s="5" t="n"/>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>5fc9b9b34ef5170001a575db</t>
         </is>
@@ -4158,15 +4280,20 @@
       <c r="M58" s="5" t="n"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>City from raw_address; Apollo returned no city field.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>680f881ce54df2001d30bb09</t>
         </is>
@@ -4219,17 +4346,18 @@
         </is>
       </c>
       <c r="M59" s="5" t="n"/>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>63cd7a9ed41f2800016a6fed</t>
         </is>
@@ -4282,17 +4410,18 @@
         </is>
       </c>
       <c r="M60" s="5" t="n"/>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>65ae54f690683d031a5e8d74</t>
         </is>
@@ -4345,17 +4474,18 @@
         </is>
       </c>
       <c r="M61" s="5" t="n"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>5e57084e5ec9c30001a83b26</t>
         </is>
@@ -4408,17 +4538,18 @@
         </is>
       </c>
       <c r="M62" s="5" t="n"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N62" s="2" t="n"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>5d6ff2bf9b175800d273dbd9</t>
         </is>
@@ -4471,17 +4602,18 @@
         </is>
       </c>
       <c r="M63" s="5" t="n"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N63" s="2" t="n"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>6740584c70d0c60001d0c885</t>
         </is>
@@ -4534,17 +4666,18 @@
         </is>
       </c>
       <c r="M64" s="5" t="n"/>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>5569c21b7369642571ff8700</t>
         </is>
@@ -4597,17 +4730,18 @@
         </is>
       </c>
       <c r="M65" s="5" t="n"/>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N65" s="2" t="n"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>55923e4773696448593f8f00</t>
         </is>
@@ -4662,15 +4796,20 @@
       <c r="M66" s="5" t="n"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>City from raw_address; Apollo returned no city field.</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>64d6198be64f72008bd4844c</t>
         </is>
@@ -4723,17 +4862,18 @@
         </is>
       </c>
       <c r="M67" s="5" t="n"/>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N67" s="2" t="n"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>6006e7a72a0c2c018cbddee9</t>
         </is>
@@ -4786,17 +4926,18 @@
         </is>
       </c>
       <c r="M68" s="5" t="n"/>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N68" s="2" t="n"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
         <is>
           <t>68a810a4e9d1e20021add8b4</t>
         </is>
@@ -4851,15 +4992,20 @@
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Facility-services coordinator. Phone is a 630 Illinois area code despite the NJ address.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>54a12b1e69702d8cfc6f9f02</t>
         </is>
@@ -4914,15 +5060,20 @@
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Phone is a 630 Illinois area code despite the NJ address.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>5fc915921406c90001735d8a</t>
         </is>
@@ -4975,17 +5126,18 @@
         </is>
       </c>
       <c r="M71" s="5" t="n"/>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N71" s="2" t="n"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
         <is>
           <t>6505493b291a99000174024a</t>
         </is>
@@ -5040,15 +5192,20 @@
       <c r="M72" s="5" t="n"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Electrical wholesaler, not a contractor. Acquired by U.S. Electrical Services.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>54a1396069702d2851f55800</t>
         </is>
@@ -5101,17 +5258,18 @@
         </is>
       </c>
       <c r="M73" s="5" t="n"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>5da47cbba3b18d00018b2439</t>
         </is>
@@ -5166,15 +5324,20 @@
       <c r="M74" s="5" t="n"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Shares its phone and address with Academy Service Group (batch 3) - likely affiliated entities.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>54a25d837468693cdd2c341d</t>
         </is>
@@ -5227,17 +5390,18 @@
         </is>
       </c>
       <c r="M75" s="5" t="n"/>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N75" s="2" t="n"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>54a121b169702d8ed41fc302</t>
         </is>
@@ -5292,15 +5456,20 @@
       <c r="M76" s="5" t="n"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Plumbing wholesaler, not a contractor.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>54a1b7de74686945fa9aaa0a</t>
         </is>
@@ -5355,15 +5524,20 @@
       <c r="M77" s="5" t="n"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Recruiting firm, not a contractor.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>618938cda5a7370001f9ad5e</t>
         </is>
@@ -5418,15 +5592,20 @@
       <c r="M78" s="5" t="n"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Consulting engineering firm, not a trade contractor.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>55f4bc4af3e5bb165f001a64</t>
         </is>
@@ -5481,15 +5660,20 @@
       <c r="M79" s="5" t="n"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Plumbing wholesaler, not a contractor. Phone is a 718 Brooklyn area code; HQ described as Brooklyn NY.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>5b874bbaf874f74b55cd0379</t>
         </is>
@@ -5544,15 +5728,20 @@
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Consulting engineering firm, not a trade contractor.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>55f60f66f3e5bb1d02001ebc</t>
         </is>
@@ -5607,15 +5796,20 @@
       <c r="M81" s="5" t="n"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Apollo reports a Fairfield NJ address but raw_address is 'worldwide flooring company, dk', the phone is a +44 UK number and the company is described as Danish. NJ geography filter will pass it incorrectly.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>5569e632736964256532b000</t>
         </is>
@@ -5670,15 +5864,20 @@
       <c r="M82" s="5" t="n"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Equipment distributor, not a contractor.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>5da6d80bb076420001834e26</t>
         </is>
@@ -5731,17 +5930,18 @@
         </is>
       </c>
       <c r="M83" s="5" t="n"/>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N83" s="2" t="n"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>5da3f6463a4e680001cb40c8</t>
         </is>
@@ -5794,17 +5994,18 @@
         </is>
       </c>
       <c r="M84" s="5" t="n"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>apollo.io/organizations</t>
-        </is>
-      </c>
+      <c r="N84" s="2" t="n"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
         <is>
           <t>5cb361faf65125bb20e89f6a</t>
         </is>
@@ -5859,15 +6060,20 @@
       <c r="M85" s="5" t="n"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Plumbing wholesaler, not a contractor.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
         <is>
           <t>54fca5617369647fc2433300</t>
         </is>
@@ -5922,15 +6128,20 @@
       <c r="M86" s="5" t="n"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>E-commerce filter retailer, not a contractor.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
         <is>
           <t>5f238ac86d324800c02fac43</t>
         </is>
@@ -5985,15 +6196,20 @@
       <c r="M87" s="5" t="n"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Marketing agency serving roofers, not a contractor.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>5569922473696425712a5600</t>
         </is>
@@ -6048,22 +6264,27 @@
       <c r="M88" s="5" t="n"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>apollo.io/organizations</t>
+          <t>Trade association, not a contractor.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:50:54+00:00</t>
+          <t>apollo.io/organizations</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
+          <t>2026-09-19T17:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
           <t>54a1361669702d3cbba52601</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P88"/>
+  <autoFilter ref="A1:Q88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
